--- a/www/ig/fhir/mesures/StructureDefinition-mesures-observation-glucose.xlsx
+++ b/www/ig/fhir/mesures/StructureDefinition-mesures-observation-glucose.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$131</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$120</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5039" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4619" uniqueCount="701">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T08:41:57+00:00</t>
+    <t>2026-02-18T13:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,11 +84,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil de la ressource Observation pour définir une Glycémie
-Ce profil permet de gérer 4 types d'indicateurs de glycémie:
+    <t>Profil biologie de la ressource Observation pour définir une Glycémie
+Ce profil permet de gérer 3 types d'indicateurs de glycémie:
 - le taux de glucose sanguin, mesuré en mg/dl
 - le taux de glucose interstitiel, mesuré en mg/dl
-- l’hémoglobine glyquée (Hb1Ac) mesurée en %
 - l’index de gestion de glycémie (IGG) qui procure une estimation de l’HbA1c également mesuré en %
 L'extension MesNumberOfDays permet de spécifier le nombre de jours dans la mesure du taux de glucose interstitiel et de l’index de gestion de glycémie (IGG) .
 L'extension MesMomentOfMeasurement (contexte de la mesure) est utilisée dans le cas de la mesure du glucose sanguin.</t>
@@ -446,7 +445,7 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -462,7 +461,7 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -500,7 +499,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -524,7 +523,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -567,7 +566,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -650,7 +649,7 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
   </si>
   <si>
     <t>Observation.extension:MesReasonForMeasurement</t>
@@ -666,13 +665,31 @@
     <t>Motif de la mesure</t>
   </si>
   <si>
-    <t>Extension du Motif de la mesure, exprimé en texte libre  (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…).</t>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Observation.extension:mes-original-data</t>
+  </si>
+  <si>
+    <t>mes-original-data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-original-data}
+</t>
+  </si>
+  <si>
+    <t>Valeur d'origine de la donnée. Cette extension est présente uniquement si le résultat contenu dans Observation.value provient d'une conversion (par ex. g/L converti en mmol/L)</t>
+  </si>
+  <si>
+    <t>Extension permettant de renseigner la donnée originale. 
+Dans le cas où une conversion d'unité a été effectuée sur la valeur de la mesure, cette extension permet de conserver la valeur originale telle que mesurée par le dispositif.</t>
+  </si>
+  <si>
     <t>Observation.extension:MesMomentOfMeasurement</t>
   </si>
   <si>
@@ -969,19 +986,6 @@
 Utilisé pour les mesures du taux de glucose interstitiel et l’index de gestion de glycémie.</t>
   </si>
   <si>
-    <t>Observation.extension:MesDiabetisType</t>
-  </si>
-  <si>
-    <t>MesDiabetisType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-diabetis-type}
-</t>
-  </si>
-  <si>
-    <t>Type de diabète</t>
-  </si>
-  <si>
     <t>Observation.modifierExtension</t>
   </si>
   <si>
@@ -1033,7 +1037,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1062,7 +1066,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -1135,7 +1139,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1236,7 +1240,6 @@
     <t>Types de glycémie:
 • Glucose sanguin
 • Glucose interstitiel
-• Hémoglobine glyquée (HbA1c)
 • Index de gestion de glycémie (IGG)</t>
   </si>
   <si>
@@ -1337,7 +1340,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1455,7 +1458,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -1665,7 +1668,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1730,7 +1733,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1786,7 +1789,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1804,7 +1807,7 @@
     <t>Observation.method</t>
   </si>
   <si>
-    <t>How it was done</t>
+    <t>La méthode de mesure du cholestérol total est fortement conseillée pour déterminer si des résultats sont comparables et ainsi interpréter cette donnée.</t>
   </si>
   <si>
     <t>Indicates the mechanism used to perform the observation.</t>
@@ -1828,7 +1831,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1889,7 +1892,7 @@
 </t>
   </si>
   <si>
-    <t>Provides guide for interpretation</t>
+    <t>Associer la mesure à l'intervalle de référence est fortement recommandé pour interpréter le résultat par rapport à la norme, qui peut varier selon de nombreux critères : la méthode d'analyse, l'age, le sexe, ...</t>
   </si>
   <si>
     <t>Guidance on how to interpret the value by comparison to a normal or recommended range.  Multiple reference ranges are interpreted as an "OR".   In other words, to represent two distinct target populations, two `referenceRange` elements would be used.</t>
@@ -1937,7 +1940,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1987,7 +1990,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -2017,43 +2020,10 @@
     <t>Need to be able to identify the target population for proper interpretation.</t>
   </si>
   <si>
-    <t>JDV_J148-ReferenceRangeAppliesTo-CISIS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J148-ReferenceRangeAppliesTo-CISIS/FHIR/JDV-J148-ReferenceRangeAppliesTo-CISIS</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo.text</t>
+    <t>Codes identifying the population the reference range applies to.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -2090,7 +2060,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2112,7 +2082,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2177,7 +2147,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2556,20 +2526,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP131"/>
+  <dimension ref="A1:AP120"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="75.6015625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="56.09375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="64.81640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.26953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="223.14453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2578,28 +2548,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="112.42578125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="78.68359375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4918,7 +4888,7 @@
         <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -5004,12 +4974,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
       </c>
@@ -5030,13 +5002,13 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>109</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5087,19 +5059,19 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>110</v>
+        <v>196</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>82</v>
+        <v>207</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>82</v>
@@ -5111,7 +5083,7 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -5122,10 +5094,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5136,7 +5108,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -5148,13 +5120,13 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>195</v>
+        <v>109</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5193,31 +5165,31 @@
         <v>82</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>82</v>
@@ -5229,7 +5201,7 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -5240,10 +5212,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5251,10 +5223,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>82</v>
@@ -5266,24 +5238,22 @@
         <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="S23" t="s" s="2">
         <v>82</v>
@@ -5313,31 +5283,31 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>121</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -5349,7 +5319,7 @@
         <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>192</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5360,10 +5330,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5371,7 +5341,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>93</v>
@@ -5386,22 +5356,24 @@
         <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L24" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>82</v>
@@ -5419,11 +5391,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5441,10 +5415,10 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>93</v>
@@ -5453,7 +5427,7 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5476,10 +5450,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5502,13 +5476,13 @@
         <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>107</v>
+        <v>230</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>109</v>
+        <v>232</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -5535,13 +5509,11 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>234</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5559,7 +5531,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>110</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5571,7 +5543,7 @@
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -5583,7 +5555,7 @@
         <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>111</v>
+        <v>192</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5594,21 +5566,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -5620,17 +5592,15 @@
         <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5667,31 +5637,31 @@
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5714,21 +5684,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -5737,23 +5707,21 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>237</v>
+        <v>115</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>238</v>
+        <v>116</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5789,19 +5757,19 @@
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>241</v>
+        <v>121</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5813,7 +5781,7 @@
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5822,10 +5790,10 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>242</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>243</v>
+        <v>111</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5836,10 +5804,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5859,19 +5827,23 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>108</v>
+        <v>242</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5919,19 +5891,19 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>110</v>
+        <v>246</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5940,10 +5912,10 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>111</v>
+        <v>248</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5954,21 +5926,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5980,17 +5952,15 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -6027,31 +5997,31 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -6074,21 +6044,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -6097,23 +6067,21 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>251</v>
+        <v>116</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -6149,31 +6117,31 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>254</v>
+        <v>121</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6182,10 +6150,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>256</v>
+        <v>111</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6196,10 +6164,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6207,7 +6175,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>93</v>
@@ -6222,18 +6190,20 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6281,7 +6251,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6302,10 +6272,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6316,10 +6286,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6327,7 +6297,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>93</v>
@@ -6342,18 +6312,18 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6401,7 +6371,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6422,10 +6392,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6436,10 +6406,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6447,7 +6417,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>93</v>
@@ -6462,17 +6432,17 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6521,7 +6491,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6542,10 +6512,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6556,10 +6526,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6582,19 +6552,17 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>283</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6643,7 +6611,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6664,10 +6632,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6678,10 +6646,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6704,19 +6672,19 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>107</v>
+        <v>288</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6765,7 +6733,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6786,10 +6754,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6800,14 +6768,12 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6825,19 +6791,23 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>302</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>299</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6885,19 +6855,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>196</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6906,10 +6876,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>82</v>
+        <v>303</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6954,7 +6924,7 @@
         <v>308</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7040,10 +7010,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7069,16 +7039,16 @@
         <v>114</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7127,7 +7097,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7162,10 +7132,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7188,17 +7158,17 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7247,7 +7217,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7262,19 +7232,19 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -7282,14 +7252,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7308,17 +7278,17 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7367,7 +7337,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7382,16 +7352,16 @@
         <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7402,14 +7372,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7428,16 +7398,16 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7487,7 +7457,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7502,16 +7472,16 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7520,12 +7490,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7551,16 +7521,16 @@
         <v>169</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7585,11 +7555,11 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7607,7 +7577,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>93</v>
@@ -7622,19 +7592,19 @@
         <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7642,10 +7612,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7668,19 +7638,19 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7708,16 +7678,16 @@
         <v>173</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7727,7 +7697,7 @@
         <v>120</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7751,24 +7721,24 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>82</v>
@@ -7790,19 +7760,19 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7830,10 +7800,10 @@
         <v>173</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>82</v>
@@ -7851,7 +7821,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7875,10 +7845,10 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7886,10 +7856,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8004,10 +7974,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8122,12 +8092,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8153,16 +8123,16 @@
         <v>147</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -8211,7 +8181,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8232,10 +8202,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8246,10 +8216,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8364,10 +8334,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8482,12 +8452,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8513,23 +8483,23 @@
         <v>135</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>82</v>
@@ -8571,7 +8541,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8592,10 +8562,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8606,10 +8576,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8635,13 +8605,13 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8691,7 +8661,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8712,10 +8682,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8724,12 +8694,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8755,21 +8725,21 @@
         <v>169</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>82</v>
@@ -8811,7 +8781,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8832,10 +8802,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8846,10 +8816,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8875,14 +8845,14 @@
         <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8892,7 +8862,7 @@
         <v>82</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>82</v>
@@ -8931,7 +8901,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8952,10 +8922,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8966,10 +8936,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8992,19 +8962,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9053,7 +9023,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -9074,10 +9044,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -9088,10 +9058,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9117,16 +9087,16 @@
         <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9175,7 +9145,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9196,10 +9166,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -9208,16 +9178,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9236,19 +9206,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9277,7 +9247,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9295,7 +9265,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>93</v>
@@ -9310,30 +9280,30 @@
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9448,10 +9418,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9568,10 +9538,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9597,16 +9567,16 @@
         <v>147</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9655,7 +9625,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9676,10 +9646,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9690,10 +9660,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9808,10 +9778,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9928,10 +9898,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9957,16 +9927,16 @@
         <v>135</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -10015,7 +9985,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -10036,10 +10006,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -10050,10 +10020,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10079,13 +10049,13 @@
         <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10135,7 +10105,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10156,10 +10126,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10170,10 +10140,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10199,14 +10169,14 @@
         <v>169</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
@@ -10255,7 +10225,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10276,10 +10246,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10290,10 +10260,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10319,14 +10289,14 @@
         <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10375,7 +10345,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10396,10 +10366,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10410,10 +10380,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10436,19 +10406,19 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10497,7 +10467,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10518,10 +10488,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10532,10 +10502,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10561,16 +10531,16 @@
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10619,7 +10589,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10640,10 +10610,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10652,12 +10622,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10680,19 +10650,19 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10741,7 +10711,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10756,19 +10726,19 @@
         <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>82</v>
@@ -10776,10 +10746,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10802,16 +10772,16 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10861,7 +10831,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10882,13 +10852,13 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>82</v>
@@ -10896,14 +10866,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10922,19 +10892,19 @@
         <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10983,7 +10953,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10998,34 +10968,34 @@
         <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11044,19 +11014,19 @@
         <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -11105,7 +11075,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11114,25 +11084,25 @@
         <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>82</v>
@@ -11140,10 +11110,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11169,13 +11139,13 @@
         <v>129</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11225,7 +11195,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11246,13 +11216,13 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>82</v>
@@ -11260,10 +11230,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11286,17 +11256,17 @@
         <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11345,7 +11315,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11360,30 +11330,30 @@
         <v>105</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11406,19 +11376,19 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11467,7 +11437,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11476,7 +11446,7 @@
         <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>105</v>
@@ -11485,27 +11455,27 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11620,10 +11590,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11740,10 +11710,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11766,19 +11736,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11827,7 +11797,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11848,10 +11818,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11862,10 +11832,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11891,20 +11861,20 @@
         <v>169</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q78" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="R78" t="s" s="2">
         <v>82</v>
@@ -11925,13 +11895,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11949,7 +11919,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11970,10 +11940,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11984,10 +11954,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12013,14 +11983,14 @@
         <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -12069,7 +12039,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12090,10 +12060,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12104,10 +12074,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12133,14 +12103,14 @@
         <v>135</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12150,7 +12120,7 @@
         <v>82</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>82</v>
@@ -12189,7 +12159,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12198,7 +12168,7 @@
         <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>105</v>
@@ -12210,10 +12180,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12224,10 +12194,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12253,16 +12223,16 @@
         <v>169</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12287,13 +12257,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12311,7 +12281,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12332,10 +12302,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12344,12 +12314,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12372,19 +12342,19 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12412,10 +12382,10 @@
         <v>151</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12433,7 +12403,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12442,7 +12412,7 @@
         <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>105</v>
@@ -12457,7 +12427,7 @@
         <v>192</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12468,10 +12438,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12586,10 +12556,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12706,10 +12676,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12735,16 +12705,16 @@
         <v>147</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12793,7 +12763,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12814,10 +12784,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12828,10 +12798,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12946,10 +12916,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13066,10 +13036,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13095,16 +13065,16 @@
         <v>135</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13153,7 +13123,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13174,10 +13144,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13188,10 +13158,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13217,13 +13187,13 @@
         <v>107</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13273,7 +13243,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13294,10 +13264,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13308,10 +13278,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13337,14 +13307,14 @@
         <v>169</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
@@ -13393,7 +13363,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13414,10 +13384,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13428,10 +13398,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13457,14 +13427,14 @@
         <v>107</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13513,7 +13483,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13534,10 +13504,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13548,10 +13518,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13574,19 +13544,19 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13635,7 +13605,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13656,10 +13626,10 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13670,10 +13640,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13699,16 +13669,16 @@
         <v>107</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13757,7 +13727,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13778,10 +13748,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13792,14 +13762,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13818,19 +13788,19 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13858,10 +13828,10 @@
         <v>151</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13879,7 +13849,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13897,27 +13867,27 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13940,19 +13910,19 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -14001,7 +13971,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -14022,10 +13992,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -14036,10 +14006,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14062,16 +14032,16 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14100,10 +14070,10 @@
         <v>159</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -14121,7 +14091,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14139,27 +14109,27 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14182,19 +14152,19 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -14223,7 +14193,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -14241,7 +14211,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14262,10 +14232,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14276,10 +14246,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14302,16 +14272,16 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14361,7 +14331,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14379,27 +14349,27 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14422,16 +14392,16 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14481,7 +14451,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14499,27 +14469,27 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP99" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14530,10 +14500,10 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>82</v>
@@ -14542,19 +14512,19 @@
         <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14603,7 +14573,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14615,7 +14585,7 @@
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14624,10 +14594,10 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14638,10 +14608,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14756,10 +14726,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14876,14 +14846,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14905,16 +14875,16 @@
         <v>114</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14963,7 +14933,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14998,10 +14968,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15024,13 +14994,13 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15081,7 +15051,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -15090,7 +15060,7 @@
         <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>105</v>
@@ -15102,10 +15072,10 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15116,10 +15086,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15142,13 +15112,13 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -15199,7 +15169,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15208,7 +15178,7 @@
         <v>93</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>105</v>
@@ -15220,10 +15190,10 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15234,10 +15204,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15260,19 +15230,19 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15300,10 +15270,10 @@
         <v>173</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -15321,7 +15291,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15339,13 +15309,13 @@
         <v>82</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15356,10 +15326,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15382,19 +15352,19 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15419,13 +15389,13 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>228</v>
+        <v>159</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15443,7 +15413,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15461,13 +15431,13 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15478,10 +15448,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15504,16 +15474,18 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>107</v>
+        <v>643</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>108</v>
+        <v>644</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>109</v>
+        <v>645</v>
       </c>
       <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
       </c>
@@ -15561,7 +15533,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>110</v>
+        <v>642</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15573,7 +15545,7 @@
         <v>82</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>82</v>
@@ -15585,7 +15557,7 @@
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>111</v>
+        <v>647</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15596,21 +15568,21 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>82</v>
@@ -15622,17 +15594,15 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>115</v>
+        <v>649</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15669,31 +15639,31 @@
         <v>82</v>
       </c>
       <c r="AB109" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC109" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE109" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>121</v>
+        <v>648</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>82</v>
@@ -15702,10 +15672,10 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>82</v>
+        <v>620</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>111</v>
+        <v>651</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15716,10 +15686,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15742,20 +15712,18 @@
         <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>147</v>
+        <v>653</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>237</v>
+        <v>654</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>238</v>
+        <v>655</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>656</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15803,7 +15771,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>241</v>
+        <v>652</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15824,10 +15792,10 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>242</v>
+        <v>657</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>243</v>
+        <v>658</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15838,10 +15806,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>644</v>
+        <v>659</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15852,7 +15820,7 @@
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
@@ -15861,18 +15829,20 @@
         <v>82</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>107</v>
+        <v>660</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>108</v>
+        <v>661</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>663</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15921,19 +15891,19 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>110</v>
+        <v>659</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>82</v>
@@ -15942,10 +15912,10 @@
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>82</v>
+        <v>657</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>111</v>
+        <v>664</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>82</v>
@@ -15954,16 +15924,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15973,27 +15943,29 @@
         <v>81</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>114</v>
+        <v>600</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>115</v>
+        <v>666</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>116</v>
+        <v>666</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O112" s="2"/>
+        <v>667</v>
+      </c>
+      <c r="O112" t="s" s="2">
+        <v>668</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
       </c>
@@ -16029,19 +16001,19 @@
         <v>82</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>121</v>
+        <v>665</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16053,7 +16025,7 @@
         <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>122</v>
+        <v>669</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>82</v>
@@ -16062,10 +16034,10 @@
         <v>82</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>82</v>
+        <v>670</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>111</v>
+        <v>671</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16076,10 +16048,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>646</v>
+        <v>672</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>646</v>
+        <v>672</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16087,7 +16059,7 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
         <v>93</v>
@@ -16099,23 +16071,19 @@
         <v>82</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>250</v>
+        <v>108</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>82</v>
       </c>
@@ -16163,7 +16131,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>254</v>
+        <v>110</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -16175,7 +16143,7 @@
         <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>82</v>
@@ -16184,10 +16152,10 @@
         <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>256</v>
+        <v>111</v>
       </c>
       <c r="AO113" t="s" s="2">
         <v>82</v>
@@ -16198,21 +16166,21 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>647</v>
+        <v>673</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>647</v>
+        <v>673</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>82</v>
@@ -16221,19 +16189,19 @@
         <v>82</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>259</v>
+        <v>115</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>260</v>
+        <v>116</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>261</v>
+        <v>117</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16283,19 +16251,19 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>262</v>
+        <v>121</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>82</v>
@@ -16304,10 +16272,10 @@
         <v>82</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>263</v>
+        <v>82</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>264</v>
+        <v>111</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>82</v>
@@ -16318,43 +16286,45 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>648</v>
+        <v>674</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>648</v>
+        <v>674</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>82</v>
+        <v>611</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J115" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>169</v>
+        <v>114</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>267</v>
+        <v>612</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>613</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O115" t="s" s="2">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16403,19 +16373,19 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>270</v>
+        <v>614</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>82</v>
@@ -16424,10 +16394,10 @@
         <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>271</v>
+        <v>82</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>272</v>
+        <v>192</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
@@ -16436,12 +16406,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
-        <v>649</v>
+        <v>675</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>649</v>
+        <v>675</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16449,13 +16419,13 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>82</v>
@@ -16464,17 +16434,19 @@
         <v>94</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>107</v>
+        <v>230</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>275</v>
+        <v>676</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N116" s="2"/>
+        <v>677</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>678</v>
+      </c>
       <c r="O116" t="s" s="2">
-        <v>277</v>
+        <v>679</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16499,13 +16471,13 @@
         <v>82</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>82</v>
+        <v>680</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>82</v>
+        <v>681</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>82</v>
@@ -16523,10 +16495,10 @@
         <v>82</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>278</v>
+        <v>675</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>93</v>
@@ -16541,27 +16513,27 @@
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>82</v>
+        <v>682</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>279</v>
+        <v>398</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>280</v>
+        <v>399</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
-        <v>650</v>
+        <v>683</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>650</v>
+        <v>683</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16575,7 +16547,7 @@
         <v>93</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>82</v>
@@ -16584,19 +16556,19 @@
         <v>94</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>283</v>
+        <v>684</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>284</v>
+        <v>685</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>285</v>
+        <v>686</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>286</v>
+        <v>687</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>287</v>
+        <v>473</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16621,13 +16593,13 @@
         <v>82</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>82</v>
+        <v>688</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>82</v>
+        <v>689</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>82</v>
@@ -16645,7 +16617,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>288</v>
+        <v>683</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16654,7 +16626,7 @@
         <v>93</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>82</v>
+        <v>690</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>105</v>
@@ -16663,27 +16635,27 @@
         <v>82</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>82</v>
+        <v>691</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>289</v>
+        <v>476</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>290</v>
+        <v>477</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
-        <v>651</v>
+        <v>692</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>651</v>
+        <v>692</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16697,28 +16669,28 @@
         <v>93</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>107</v>
+        <v>230</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>293</v>
+        <v>693</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>294</v>
+        <v>694</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>295</v>
+        <v>695</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>296</v>
+        <v>527</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>82</v>
@@ -16743,13 +16715,13 @@
         <v>82</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>82</v>
+        <v>529</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>82</v>
@@ -16767,7 +16739,7 @@
         <v>82</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>297</v>
+        <v>692</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -16776,7 +16748,7 @@
         <v>93</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>82</v>
+        <v>696</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>105</v>
@@ -16788,10 +16760,10 @@
         <v>82</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>298</v>
+        <v>192</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>299</v>
+        <v>531</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>82</v>
@@ -16802,21 +16774,21 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>652</v>
+        <v>697</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>652</v>
+        <v>697</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>82</v>
@@ -16828,17 +16800,19 @@
         <v>82</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>653</v>
+        <v>230</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>654</v>
+        <v>545</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>546</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>547</v>
+      </c>
       <c r="O119" t="s" s="2">
-        <v>656</v>
+        <v>548</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>82</v>
@@ -16863,13 +16837,13 @@
         <v>82</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="Y119" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
       <c r="Z119" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>82</v>
@@ -16887,13 +16861,13 @@
         <v>82</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>652</v>
+        <v>697</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>82</v>
@@ -16905,27 +16879,27 @@
         <v>82</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>82</v>
+        <v>552</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>657</v>
+        <v>553</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>82</v>
+        <v>554</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>658</v>
+        <v>698</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>658</v>
+        <v>698</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16936,7 +16910,7 @@
         <v>80</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>82</v>
@@ -16948,16 +16922,20 @@
         <v>82</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>659</v>
+        <v>699</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
+        <v>700</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>604</v>
+      </c>
       <c r="P120" t="s" s="2">
         <v>82</v>
       </c>
@@ -17005,13 +16983,13 @@
         <v>82</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>658</v>
+        <v>698</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>82</v>
@@ -17026,1362 +17004,30 @@
         <v>82</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>661</v>
+        <v>607</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP124" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP126" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="P127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AP127" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="P128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP128" t="s" s="2">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="P129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP129" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="130" hidden="true">
-      <c r="A130" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="P130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL130" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP130" t="s" s="2">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="P131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP131" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP131">
-    <filterColumn colId="6">
+  <autoFilter ref="A1:AP120">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI130">
+  <conditionalFormatting sqref="A2:AI119">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
